--- a/deliverables/exports/track-b/09-pricing-packaging.xlsx
+++ b/deliverables/exports/track-b/09-pricing-packaging.xlsx
@@ -10,12 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.1 Value metric selection" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.2 Pricing tiers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="The billing shape constraint" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="The affordability tension" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anchor 1. Cost of the problem" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anchor 2. Alternative" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anchor 3. Breakeven, restated" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carried forward" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.2 Pricing tiers (2)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="The billing shape constraint" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="The affordability tension" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anchor 1. Cost of the problem" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anchor 2. Alternative" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anchor 3. Breakeven, restated" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carried forward" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -486,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -670,196 +671,295 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>**Room is a genuine decoy.** It contains the commodity half of the offer, courses and a room, which Phase 1 scored as table stakes and which free alternatives already cover. Its job is to make Deal look correct. A member who buys Room and never brings a deal is the member most likely to churn in 14 days, so Room should be priced close enough to Deal that choosing it feels like a false economy.</t>
+          <t>**The tiers now map to the bands.** Per `00-RESOLUTIONS.md` conflict 2, the offer is the movement between bands, so the tiers should describe how far up a member is being carried rather than how much content they receive.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>**Direct exists to be mostly unavailable.** Phase 1 found one to ones are the worst item in the set on delivery effort, and Phase 2 found founder access is the most praised and first to vanish across the whole category. Publishing the slot count and closing the tier when it fills is both the honest answer and the better commercial one.</t>
+          <t>This also fixes a weakness in the old tier logic. Room was justified only as a decoy. It now has an honest job: it carries a member through the rungs that cost nothing but knowledge, which is genuinely most of band 1 to 2. A member who never needs more than that has still been served, which is a better retention story than a tier designed to look wrong.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Expansion levers</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>**Room is a genuine decoy.** It contains the commodity half of the offer, courses and a room, which Phase 1 scored as table stakes and which free alternatives already cover. Its job is to make Deal look correct. A member who buys Room and never brings a deal is the member most likely to churn in 14 days, so Room should be priced close enough to Deal that choosing it feels like a false economy.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>• Room to Deal, triggered by a live deal. The upgrade prompt is the member</t>
+          <t>**Direct exists to be mostly unavailable.** Phase 1 found one to ones are the worst item in the set on delivery effort, and Phase 2 found founder access is the most praised and first to vanish across the whole category. Publishing the slot count and closing the tier when it fills is both the honest answer and the better commercial one.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>posting about a real deal. That is a behavioural trigger, not a calendar one.</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Expansion levers</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>• Deal to Direct, triggered by a stalled deal. A member whose deal is stuck</t>
+          <t>• Room to Deal, triggered by a live deal. The upgrade prompt is the member</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>after a teardown is the person for whom one to one is genuinely worth it.</t>
+          <t>posting about a real deal. That is a behavioural trigger, not a calendar one.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>• Monthly to annual, triggered by payment friction. See below. This lever is</t>
+          <t>• Deal to Direct, triggered by a stalled deal. A member whose deal is stuck</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>unusual in that it improves the member's experience and the business's cash at the same time.</t>
+          <t>after a teardown is the person for whom one to one is genuinely worth it.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>The billing shape constraint</t>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>• Monthly to annual, triggered by payment friction. See below. This lever is</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
+          <t>unusual in that it improves the member's experience and the business's cash at the same time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>The billing shape constraint</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
           <t>This is not a footnote. In Egypt, monthly USD card caps are reported as low as $50 to $200 and international card limits are reported suspended on debit cards. A recurring monthly USD card charge is unreliable in one of the largest origin markets by developer population, and it fails silently at renewal rather than at signup.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>**Do not price this as a monthly USD subscription and plan to solve payments later.** The tiers above should be quoted annually or per cohort first, with monthly as the option rather than the default.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>The affordability tension, held rather than deferred</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>A price set against what the offer is worth in a target market is a significant amount of money at a local income. A price set against local income will not sustain the founder time the Deal and Direct tiers require. Both are true at once.</t>
+          <t>**Do not price this as a monthly USD subscription and plan to solve payments later.** The tiers above should be quoted annually or per cohort first, with monthly as the option rather than the default.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>**Recommendation: one public price list, plus a stated founding cohort rate, plus a small explicit scholarship allocation.** Regional pricing inside a single visible community is the option most likely to produce a public argument, precisely because the members can see each other. This is a founder decision, not a model decision, and it should be made before launch rather than after the first complaint.</t>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>The affordability tension, held rather than deferred</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>A price set against what the offer is worth in a target market is a significant amount of money at a local income. A price set against local income will not sustain the founder time the Deal and Direct tiers require. Both are true at once.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Step 9.3. ROI anchoring</t>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>**Recommendation: one public price list, plus a stated founding cohort rate, plus a small explicit scholarship allocation.** Regional pricing inside a single visible community is the option most likely to produce a public argument, precisely because the members can see each other. This is a founder decision, not a model decision, and it should be made before launch rather than after the first complaint.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Step 9.3. ROI anchoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
           <t>**The skill's "one outcome pays for X years" calculator is dropped for Track B.** `SKILL-ADAPTATION.md` is explicit: pricing a training product on the member's earned outcome is an income claim. The calculator is that claim expressed as arithmetic. It does not appear in this phase, in Phase 6, in Phase 8, or in the deck.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>What replaces it is anchoring on cost and effort that can be stated without claiming anyone's result.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Anchor 1. Cost of the problem, stated without income figures</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Every cell is `{TBD}` and filled by the member, not by the business. The scorecard is where this data comes from, which is one more reason it asks about deals rather than about knowledge.</t>
+          <t>What replaces it is anchoring on cost and effort that can be stated without claiming anyone's result.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Anchor 2. Alternative comparison</t>
+          <t>Anchor 1. Cost of the problem, stated without income figures</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>The marketplace row is the strongest one available and it is entirely factual. A commission is a real, recurring, percentage cost that continues for as long as the member uses the platform. Stating it is not an income claim.</t>
+          <t>Every cell is `{TBD}` and filled by the member, not by the business. The scorecard is where this data comes from, which is one more reason it asks about deals rather than about knowledge.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Anchor 3. Breakeven, restated</t>
+          <t>Anchor 2. Alternative comparison</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>The skill's breakeven table asks for typical customer value, which is an income figure this business must not supply. Restated as an effort breakeven.</t>
+          <t>The marketplace row is the strongest one available and it is entirely factual. A commission is a real, recurring, percentage cost that continues for as long as the member uses the platform. Stating it is not an income claim.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>Both conditions are things the member can verify about themselves. Neither requires anyone to state what they earned.</t>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Anchor 3. Breakeven, restated</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
+          <t>The skill's breakeven table asks for typical customer value, which is an income figure this business must not supply. Restated as an effort breakeven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Both conditions are things the member can verify about themselves. Neither requires anyone to state what they earned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Carried forward</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Carried forward</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Goes to</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Per member per access tier</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Phase 10 slide 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Billing shape as structural</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Phase 7 stage 4, Phase 8 payment fallback asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Affordability recommendation</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Founder decision, before launch</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Outcome calculator dropped</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Do not reintroduce in any later asset</t>
         </is>
       </c>
     </row>
@@ -1294,6 +1394,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>9.2 Pricing tiers</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Carries a member</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Checklist, free</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Nowhere. Shows the ladder</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>The scorecard returns a band. That is the hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Room</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Band 1 to band 2</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>The free-to-fix half. Legibility, scope, champion enablement, the tax form</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Deal</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Band 2 to band 3</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Where the expensive half starts, and where a live deal is required</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Band 3 and the edge of 4</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Founder hours on a specific procurement process</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1416,7 +1627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1501,7 +1712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1616,7 +1827,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1727,7 +1938,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1818,89 +2029,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Carried forward</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Output</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Goes to</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Per member per access tier</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Phase 10 slide 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Billing shape as structural</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Phase 7 stage 4, Phase 8 payment fallback asset</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Affordability recommendation</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Founder decision, before launch</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Outcome calculator dropped</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Do not reintroduce in any later asset</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>